--- a/Gitai.xlsx
+++ b/Gitai.xlsx
@@ -24085,7 +24085,7 @@
         <v>48399</v>
       </c>
       <c r="E26" t="str">
-        <v>2024-01-28</v>
+        <v>2024-01-29</v>
       </c>
       <c r="F26" t="str">
         <v>0</v>
@@ -24100,7 +24100,7 @@
         <v>Paid</v>
       </c>
       <c r="J26" t="str">
-        <v>P:34455 I:13944</v>
+        <v>P:34455 I:13944 | TXN7388832616 GB0129989356 Completed 29-01-2024</v>
       </c>
     </row>
     <row r="27">
@@ -24132,7 +24132,7 @@
         <v>Paid</v>
       </c>
       <c r="J27" t="str">
-        <v>P:34773 I:13626</v>
+        <v>P:34773 I:13626 | TXN5863354926 Failed then TXN5906895034 GB0228746203 Completed 28-02-2024</v>
       </c>
     </row>
     <row r="28">
@@ -24187,16 +24187,16 @@
         <v>0</v>
       </c>
       <c r="G29" t="str">
-        <v>0</v>
+        <v>1620</v>
       </c>
       <c r="H29" t="str">
-        <v>48399</v>
+        <v>50019</v>
       </c>
       <c r="I29" t="str">
         <v>Paid</v>
       </c>
       <c r="J29" t="str">
-        <v>P:35418 I:12981</v>
+        <v>P:35418 I:12981 | TXN4828640519 GB0504159679 penalty ₹1,620 Completed 04-05-2024</v>
       </c>
     </row>
     <row r="30">
@@ -24277,22 +24277,22 @@
         <v>48399</v>
       </c>
       <c r="E32" t="str">
-        <v>2024-07-28</v>
+        <v>2024-07-31</v>
       </c>
       <c r="F32" t="str">
-        <v>0</v>
+        <v>895</v>
       </c>
       <c r="G32" t="str">
         <v>0</v>
       </c>
       <c r="H32" t="str">
-        <v>48399</v>
+        <v>49294</v>
       </c>
       <c r="I32" t="str">
         <v>Paid</v>
       </c>
       <c r="J32" t="str">
-        <v>P:36408 I:11991</v>
+        <v>P:36408 I:11991 | TXN3578603114 GB0731619886 Completed 31-07-2024; TXN4289021146 fee ₹119 02-08-2024</v>
       </c>
     </row>
     <row r="33">
@@ -24341,22 +24341,22 @@
         <v>48399</v>
       </c>
       <c r="E34" t="str">
-        <v>2024-09-28</v>
+        <v>2024-10-11</v>
       </c>
       <c r="F34" t="str">
-        <v>0</v>
+        <v>1552</v>
       </c>
       <c r="G34" t="str">
         <v>0</v>
       </c>
       <c r="H34" t="str">
-        <v>48399</v>
+        <v>49951</v>
       </c>
       <c r="I34" t="str">
         <v>Paid</v>
       </c>
       <c r="J34" t="str">
-        <v>P:37083 I:11316</v>
+        <v>P:37083 I:11316 | TXN8333159583 GB1011464183 Completed 11-10-2024 (13 days late)</v>
       </c>
     </row>
     <row r="35">
@@ -24373,22 +24373,22 @@
         <v>48399</v>
       </c>
       <c r="E35" t="str">
-        <v>2024-10-28</v>
+        <v>2024-10-29</v>
       </c>
       <c r="F35" t="str">
-        <v>0</v>
+        <v>736</v>
       </c>
       <c r="G35" t="str">
         <v>0</v>
       </c>
       <c r="H35" t="str">
-        <v>48399</v>
+        <v>49135</v>
       </c>
       <c r="I35" t="str">
         <v>Paid</v>
       </c>
       <c r="J35" t="str">
-        <v>P:37426 I:10973</v>
+        <v>P:37426 I:10973 | TXN8787846197+8829566659 Failed then TXN8973323525 GB1029353789 Completed 29-10-2024</v>
       </c>
     </row>
     <row r="36">
@@ -24437,22 +24437,22 @@
         <v>48399</v>
       </c>
       <c r="E37" t="str">
-        <v>2024-12-28</v>
+        <v>2025-01-07</v>
       </c>
       <c r="F37" t="str">
-        <v>0</v>
+        <v>2068</v>
       </c>
       <c r="G37" t="str">
         <v>0</v>
       </c>
       <c r="H37" t="str">
-        <v>48399</v>
+        <v>50467</v>
       </c>
       <c r="I37" t="str">
         <v>Paid</v>
       </c>
       <c r="J37" t="str">
-        <v>P:38120 I:10279</v>
+        <v>P:38120 I:10279 | TXN7560144060 Failed then TXN7703512396 GB0107818951 Completed 07-01-2025 (inst due 28-12-2024)</v>
       </c>
     </row>
     <row r="38">
@@ -24472,19 +24472,19 @@
         <v>2025-01-28</v>
       </c>
       <c r="F38" t="str">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G38" t="str">
         <v>0</v>
       </c>
       <c r="H38" t="str">
-        <v>48399</v>
+        <v>48899</v>
       </c>
       <c r="I38" t="str">
         <v>Paid</v>
       </c>
       <c r="J38" t="str">
-        <v>P:38472 I:9927</v>
+        <v>P:38472 I:9927 | TXN5292297051 Failed then TXN5541168306 GB0128660234 Completed 28-01-2025</v>
       </c>
     </row>
     <row r="39">
@@ -24757,22 +24757,22 @@
         <v>48399</v>
       </c>
       <c r="E47" t="str">
-        <v>2025-10-28</v>
+        <v>2025-10-31</v>
       </c>
       <c r="F47" t="str">
-        <v>0</v>
+        <v>3660</v>
       </c>
       <c r="G47" t="str">
         <v>0</v>
       </c>
       <c r="H47" t="str">
-        <v>48399</v>
+        <v>52059</v>
       </c>
       <c r="I47" t="str">
         <v>Paid</v>
       </c>
       <c r="J47" t="str">
-        <v>P:41789 I:6610</v>
+        <v>P:41789 I:6610 | TXN6783731773 GB1031780222 Completed 31-10-2025 (3 days late)</v>
       </c>
     </row>
     <row r="48">
@@ -24836,7 +24836,7 @@
         <v>Paid</v>
       </c>
       <c r="J49" t="str">
-        <v>P:42564 I:5835</v>
+        <v>P:42564 I:5835 | Z97477458/48-1 ACH CLEAR 28-12-2025</v>
       </c>
     </row>
     <row r="50">
@@ -24868,7 +24868,7 @@
         <v>Paid</v>
       </c>
       <c r="J50" t="str">
-        <v>P:42957 I:5442</v>
+        <v>P:42957 I:5442 | Z97477458/49-1 ACH CLEAR 28-01-2026</v>
       </c>
     </row>
     <row r="51">
@@ -24900,7 +24900,7 @@
         <v>Paid</v>
       </c>
       <c r="J51" t="str">
-        <v>P:43354 I:5045</v>
+        <v>P:43354 I:5045 | Z97477458/50-1 ACH CLEAR 28-02-2026</v>
       </c>
     </row>
     <row r="52">
@@ -24917,22 +24917,22 @@
         <v>48399</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-08</v>
       </c>
       <c r="F52" t="str">
         <v>0</v>
       </c>
       <c r="G52" t="str">
-        <v>0</v>
+        <v>2029</v>
       </c>
       <c r="H52" t="str">
-        <v>48399</v>
+        <v>50428</v>
       </c>
       <c r="I52" t="str">
         <v>Paid</v>
       </c>
       <c r="J52" t="str">
-        <v>P:43754 I:4645</v>
+        <v>P:43754 I:4645 | Z97477458/51-1 ACH BOUNCE 28-03; RZ97477458/51-1 CHEQUE BOUNCE 04-04; ON357904706+707 CLEAR 08-04; ON357904710 penalty ₹2,029 10-04</v>
       </c>
     </row>
     <row r="53">
@@ -24949,22 +24949,22 @@
         <v>48399</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-04-28</v>
+        <v>2026-05-01</v>
       </c>
       <c r="F53" t="str">
-        <v>0</v>
+        <v>736</v>
       </c>
       <c r="G53" t="str">
         <v>0</v>
       </c>
       <c r="H53" t="str">
-        <v>48399</v>
+        <v>49135</v>
       </c>
       <c r="I53" t="str">
         <v>Paid</v>
       </c>
       <c r="J53" t="str">
-        <v>P:44158 I:4241</v>
+        <v>P:44158 I:4241 | Z97477458/52-1 ACH BOUNCE 28-04; TXN0202348420 GB0501140671 Completed 01-05-2026</v>
       </c>
     </row>
     <row r="54">
@@ -24981,22 +24981,22 @@
         <v>48399</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-01</v>
       </c>
       <c r="F54" t="str">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="G54" t="str">
         <v>0</v>
       </c>
       <c r="H54" t="str">
-        <v>48399</v>
+        <v>49215</v>
       </c>
       <c r="I54" t="str">
         <v>Paid</v>
       </c>
       <c r="J54" t="str">
-        <v>P:44566 I:3833</v>
+        <v>P:44566 I:3833 | Z97477458/53-1 ACH BOUNCE 28-05; TXN5744964581 GB0601768889 Completed 01-06-2026 2:50 PM</v>
       </c>
     </row>
     <row r="55">
@@ -25405,7 +25405,7 @@
         <v>Monthly</v>
       </c>
       <c r="W2" t="str">
-        <v>Asset cost ₹31,29,698 | Chola repayment schedule 13/06/2026 | Instl 18 partial ₹683.81</v>
+        <v>Chola payments synced 13/06/2026 | 53 EMIs paid | bounce/penalty logged ₹14,612 | Inst 54 due 28-06-2026</v>
       </c>
     </row>
     <row r="3">
